--- a/data/FleetAgent.xlsx
+++ b/data/FleetAgent.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FleetAttention" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FleetApprovals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FleetDecisions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FleetNotifications" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FleetHeartbeat" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetAttention" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetApprovals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetDecisions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetNotifications" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetHeartbeat" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1155,7 +1155,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="41" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>operator@example.com</t>
+          <t>mobile:operator@example.com</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>the decision expired before the laptop saw it decide again from the desk or the phone</t>
+          <t>the decision has expired, or expires later than fleet.mobile.expire_s allows decide again from the phone</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">

--- a/data/FleetAgent.xlsx
+++ b/data/FleetAgent.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetAttention" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetApprovals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetDecisions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetNotifications" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FleetHeartbeat" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FleetAttention" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FleetApprovals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FleetDecisions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FleetNotifications" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FleetHeartbeat" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -129,9 +129,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FleetAttention" displayName="FleetAttention" ref="A1:AA4" headerRowCount="1">
-  <autoFilter ref="A1:AA4"/>
-  <tableColumns count="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FleetAttention" displayName="FleetAttention" ref="A1:AB4" headerRowCount="1">
+  <autoFilter ref="A1:AB4"/>
+  <tableColumns count="28">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="Project"/>
     <tableColumn id="3" name="Ticket"/>
@@ -159,15 +159,16 @@
     <tableColumn id="25" name="External"/>
     <tableColumn id="26" name="Digest"/>
     <tableColumn id="27" name="Seq"/>
+    <tableColumn id="28" name="Operator"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FleetApprovals" displayName="FleetApprovals" ref="A1:V4" headerRowCount="1">
-  <autoFilter ref="A1:V4"/>
-  <tableColumns count="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FleetApprovals" displayName="FleetApprovals" ref="A1:W4" headerRowCount="1">
+  <autoFilter ref="A1:W4"/>
+  <tableColumns count="23">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="Repo"/>
     <tableColumn id="3" name="Ticket"/>
@@ -190,15 +191,16 @@
     <tableColumn id="20" name="ResultCode"/>
     <tableColumn id="21" name="ResultText"/>
     <tableColumn id="22" name="SourceFile"/>
+    <tableColumn id="23" name="Operator"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FleetDecisions" displayName="FleetDecisions" ref="A1:R4" headerRowCount="1">
-  <autoFilter ref="A1:R4"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FleetDecisions" displayName="FleetDecisions" ref="A1:S4" headerRowCount="1">
+  <autoFilter ref="A1:S4"/>
+  <tableColumns count="19">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="Kind"/>
     <tableColumn id="3" name="ApprovalId"/>
@@ -217,15 +219,16 @@
     <tableColumn id="16" name="ResultCode"/>
     <tableColumn id="17" name="ResultText"/>
     <tableColumn id="18" name="ResultAt"/>
+    <tableColumn id="19" name="Operator"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FleetNotifications" displayName="FleetNotifications" ref="A1:L4" headerRowCount="1">
-  <autoFilter ref="A1:L4"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FleetNotifications" displayName="FleetNotifications" ref="A1:M4" headerRowCount="1">
+  <autoFilter ref="A1:M4"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="Repo"/>
     <tableColumn id="3" name="Ticket"/>
@@ -238,6 +241,7 @@
     <tableColumn id="10" name="Quiet"/>
     <tableColumn id="11" name="ApprovalId"/>
     <tableColumn id="12" name="SourceFile"/>
+    <tableColumn id="13" name="Operator"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -557,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -587,6 +591,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="48" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,6 +730,11 @@
           <t>Seq</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -858,6 +868,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -991,6 +1006,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1122,6 +1142,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>903</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1164,6 +1189,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="48" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1275,6 +1301,11 @@
       <c r="V1" t="inlineStr">
         <is>
           <t>SourceFile</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Operator</t>
         </is>
       </c>
     </row>
@@ -1357,6 +1388,11 @@
           <t>rdsd-uat-jira-transition-20260926T091200Z-7f3a.json</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1455,6 +1491,11 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>luna-jira-create-20260925T160301Z-a1c9.json</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
         </is>
       </c>
     </row>
@@ -1555,6 +1596,11 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>dpm-reports-pncli-write-20260925T110000Z-33be.json</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1593,6 +1639,7 @@
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="48" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1686,6 +1733,11 @@
           <t>ResultAt</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1758,6 +1810,11 @@
           <t>2026-09-25T16:06:40Z</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1818,6 +1875,11 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1896,6 +1958,11 @@
       <c r="R4" t="inlineStr">
         <is>
           <t>2026-09-24T09:05:11Z</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1928,6 +1995,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1991,6 +2059,11 @@
           <t>SourceFile</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2049,6 +2122,11 @@
           <t>20260926T091405Z-luna-needs_human-187.json</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2111,6 +2189,11 @@
           <t>20260926T091201Z-rdsd-uat-waiting_approval-42.json</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2167,6 +2250,11 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>20260925T234012Z-dpm-reports-done-880.json</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>operator@example.com</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2275,7 @@
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2290,7 +2378,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>laptop</t>
+          <t>operator@example.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2372,7 +2460,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>laptop</t>
+          <t>operator@example.com</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2454,7 +2542,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>laptop</t>
+          <t>operator@example.com</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
